--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver1.4.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver1.4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\이기석\채팅 시스템\1구역\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E916D8-74D5-4E41-BD98-DFB2F380C793}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAE83CC-F595-4D69-92F3-81A44145B3DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개요" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="609">
   <si>
     <t>이벤트 스크립트 테이블</t>
   </si>
@@ -550,24 +550,12 @@
     <t>105XXXX</t>
   </si>
   <si>
-    <t>서브 이벤트1_1</t>
-  </si>
-  <si>
-    <t>오빠를 찾는 소녀의 이야.</t>
-  </si>
-  <si>
     <t>106XXXX</t>
   </si>
   <si>
-    <t>서브 이벤트1_2</t>
-  </si>
-  <si>
     <t>107XXXX</t>
   </si>
   <si>
-    <t>서브 이벤트1_3</t>
-  </si>
-  <si>
     <t>토사구팽당한 오빠를 구함</t>
   </si>
   <si>
@@ -577,28 +565,10 @@
     <t>108XXXX</t>
   </si>
   <si>
-    <t>서브 이벤트2_1</t>
-  </si>
-  <si>
-    <t>편의점 진상만 짚고 터는 편의점 빌런</t>
-  </si>
-  <si>
     <t>109XXXX</t>
   </si>
   <si>
-    <t>서브 이벤트2_2</t>
-  </si>
-  <si>
-    <t>편의점 빌런의 행적을 쫓는 이야기</t>
-  </si>
-  <si>
     <t>110XXXX</t>
-  </si>
-  <si>
-    <t>서브 이벤트2_3</t>
-  </si>
-  <si>
-    <t>편의점 빌런과 마주치고 그를 제압하는 이야기</t>
   </si>
   <si>
     <t>그래서</t>
@@ -1618,42 +1588,21 @@
     <t>잔소리할 사람이 있다는 건… 돌아갈 곳이 있다는 뜻 아닐까요?</t>
   </si>
   <si>
-    <t>…그런 말로 흔들리지 않거든.</t>
-  </si>
-  <si>
     <t>주변 빌런부터 제압하고 이야기하자.</t>
   </si>
   <si>
     <t>동네 빌런</t>
   </si>
   <si>
-    <t>어이 신입! 저 히어로들 네가 부른 거냐?</t>
-  </si>
-  <si>
-    <t>아, 아니거든요! 저 아직 배신 안 했거든요!</t>
-  </si>
-  <si>
     <t>약속한 사례를 생각하면, 네가 왜 여기 왔는지 정확히 들어야겠어.</t>
   </si>
   <si>
     <t>사례? 그 꼬맹이가 뭘 준다고 했는데?</t>
   </si>
   <si>
-    <t>반짝이는 병뚜껑. 시장 가치가 폭락하기 전에 협조해.</t>
-  </si>
-  <si>
     <t>그 순간 창고 안쪽에서 빌런들의 고함이 들려왔다.</t>
   </si>
   <si>
-    <t>신입은 여기까지다! 공구상 위치를 알았으면 입막음해야지!</t>
-  </si>
-  <si>
-    <t>뭐? 잠깐, 나 아직 정식 계약서도 못 썼는데?</t>
-  </si>
-  <si>
-    <t>오빠는 빌런 연합에게도 버림받은 처지였다.</t>
-  </si>
-  <si>
     <t>빌런들은 오빠를 묶어 공구상 보강 작업장으로 끌고 갔다.</t>
   </si>
   <si>
@@ -1912,9 +1861,6 @@
     <t>설득 루트</t>
   </si>
   <si>
-    <t>Start_Battle_1050</t>
-  </si>
-  <si>
     <t>골목 빌런전</t>
   </si>
   <si>
@@ -1925,9 +1871,6 @@
   </si>
   <si>
     <t>보상 요구 선택 시 노출</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1Truth</t>
   </si>
   <si>
     <t>오빠의 진실 확인</t>
@@ -2061,10 +2004,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>아, 진짜. 히어로는 왜 끌고 온 거야?</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>오빠 아니거든? 나도 이제 어엿한 빌런이라고!</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -2081,6 +2020,87 @@
   </si>
   <si>
     <t>메인 이벤트 ID 호환 1020190 오류 수정</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>집 나간 오빠</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>오빠 납치극의 진실</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>토사구팽</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 진짜. 히어로가 어떻게 여길 찾은 거야?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런 말로 흔들리지 않거든.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>반짝이는 병뚜껑.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>어이 신입! 저 히어로들 네가 부른 거냐?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 아니거든요! 쟤들이 멋대로-.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 쓸어버려, 어차피 버릴 생각이었지만, 인질로 가치는 있겠지.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐? 잠깐, 아까는 영입한다면서?</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Truth\
+Start_Battle_1050</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>거짓말이 진짜가 되었네.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>오빠를 찾는 소녀의 이야rl.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점 빌런</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌런의 사연</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>나도 히어로가 되고 싶었어</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점 진상만 공격하는 편의점 빌런에 대한 소문 습득, 편의점 빌런을 추적하기 시작한다.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점 빌런과 마주치고 그를 제압하는 이야기</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의점 빌런의 행적을 추적하는 동안, 편의점 빌런의 안습한 과거사가 점점 드러난다.</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chat_Type</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2112,46 +2132,54 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Pretendard ExtraBold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -2325,7 +2353,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2436,17 +2464,30 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2459,18 +2500,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2840,123 +2869,123 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
+      <c r="B2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
@@ -2988,69 +3017,69 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
     </row>
     <row r="16" spans="2:12" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="35"/>
@@ -3158,16 +3187,16 @@
         <v>46213</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
@@ -3181,13 +3210,13 @@
         <v>46217</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="D23" s="44" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="F23" s="41"/>
       <c r="G23" s="36"/>
@@ -3241,13 +3270,13 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="8" t="s">
@@ -3255,33 +3284,33 @@
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="54"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
       <c r="E32" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
       <c r="E33" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
       <c r="E34" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
       <c r="E35" s="9" t="s">
         <v>55</v>
       </c>
@@ -3435,13 +3464,13 @@
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="D49" s="55" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="8" t="s">
@@ -3449,37 +3478,37 @@
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="53"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
       <c r="E50" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="53"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
       <c r="E51" s="18" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="47"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
       <c r="E52" s="19" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B53" s="46" t="s">
+      <c r="B53" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="50" t="s">
+      <c r="D53" s="55" t="s">
         <v>59</v>
       </c>
       <c r="E53" s="8" t="s">
@@ -3487,9 +3516,9 @@
       </c>
     </row>
     <row r="54" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="47"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
       <c r="E54" s="12" t="s">
         <v>64</v>
       </c>
@@ -3523,13 +3552,13 @@
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="48" t="s">
+      <c r="D57" s="47" t="s">
         <v>59</v>
       </c>
       <c r="E57" s="8" t="s">
@@ -3537,7 +3566,7 @@
       </c>
     </row>
     <row r="58" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="47"/>
+      <c r="B58" s="54"/>
       <c r="C58" s="49"/>
       <c r="D58" s="49"/>
       <c r="E58" s="12" t="s">
@@ -3546,14 +3575,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D31:D36"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="B2:L10"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C16:L16"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="C57:C58"/>
     <mergeCell ref="D57:D58"/>
@@ -3563,6 +3584,14 @@
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="C53:C54"/>
     <mergeCell ref="D53:D54"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D31:D36"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="B2:L10"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C16:L16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3578,7 +3607,7 @@
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="25.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="89.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3611,7 +3640,7 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="59" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
@@ -3625,7 +3654,7 @@
       </c>
     </row>
     <row r="5" spans="2:5" ht="66" x14ac:dyDescent="0.3">
-      <c r="B5" s="58"/>
+      <c r="B5" s="59"/>
       <c r="C5" t="s">
         <v>103</v>
       </c>
@@ -3637,79 +3666,79 @@
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="59" t="s">
         <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>107</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="46" t="s">
+        <v>589</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="59"/>
+      <c r="C7" t="s">
         <v>108</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D7" s="46" t="s">
+        <v>590</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="59"/>
+      <c r="C8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="58"/>
-      <c r="C7" t="s">
+      <c r="D8" s="46" t="s">
+        <v>591</v>
+      </c>
+      <c r="E8" t="s">
         <v>110</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="42" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="58"/>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>112</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" s="46" t="s">
+        <v>602</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="59"/>
+      <c r="C10" t="s">
         <v>113</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D10" s="46" t="s">
+        <v>603</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="59"/>
+      <c r="C11" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="58"/>
-      <c r="C10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="58"/>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" t="s">
-        <v>124</v>
+      <c r="D11" s="46" t="s">
+        <v>604</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -3743,7 +3772,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>41</v>
+        <v>608</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>62</v>
@@ -3774,7 +3803,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3">
@@ -3792,7 +3821,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
@@ -3808,11 +3837,11 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -3830,7 +3859,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
@@ -3846,11 +3875,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
@@ -3863,12 +3892,12 @@
         <v>1020060</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
@@ -3881,14 +3910,14 @@
         <v>1020070</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
@@ -3901,12 +3930,12 @@
         <v>1020080</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
@@ -3924,7 +3953,7 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
@@ -3940,11 +3969,11 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
@@ -3960,11 +3989,11 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="25" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
@@ -3980,11 +4009,11 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
@@ -4002,7 +4031,7 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3">
@@ -4020,7 +4049,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
@@ -4036,11 +4065,11 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3">
@@ -4056,11 +4085,11 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="25" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
@@ -4076,11 +4105,11 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
@@ -4098,7 +4127,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -4116,7 +4145,7 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
@@ -4132,11 +4161,11 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3">
@@ -4152,11 +4181,11 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
@@ -4172,11 +4201,11 @@
         <v>0</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3">
@@ -4192,11 +4221,11 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
@@ -4212,11 +4241,11 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
@@ -4234,7 +4263,7 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
@@ -4252,7 +4281,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
@@ -4270,7 +4299,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
@@ -4286,11 +4315,11 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3">
@@ -4308,7 +4337,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3">
@@ -4324,11 +4353,11 @@
         <v>0</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="25" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3">
@@ -4344,11 +4373,11 @@
         <v>0</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="25" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3">
@@ -4366,7 +4395,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="25" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3">
@@ -4379,12 +4408,12 @@
         <v>1020330</v>
       </c>
       <c r="B34" s="25">
-        <v>0</v>
-      </c>
-      <c r="C34" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="C34" s="45"/>
       <c r="D34" s="3"/>
       <c r="E34" s="25" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3">
@@ -4402,7 +4431,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3">
@@ -4420,7 +4449,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -4434,11 +4463,11 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="25" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="25">
@@ -4454,11 +4483,11 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="25">
@@ -4476,7 +4505,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="25" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="25">
@@ -4492,11 +4521,11 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="25" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="25">
@@ -4512,11 +4541,11 @@
         <v>0</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="25" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="25">
@@ -4534,7 +4563,7 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="25" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="25">
@@ -4552,7 +4581,7 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="25" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="25">
@@ -4568,11 +4597,11 @@
         <v>0</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="25" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="25">
@@ -4588,11 +4617,11 @@
         <v>0</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="25" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="25">
@@ -4610,7 +4639,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="25" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="25">
@@ -4626,11 +4655,11 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="25" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="25">
@@ -4646,11 +4675,11 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="25" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="25">
@@ -4668,7 +4697,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="25"/>
@@ -4686,7 +4715,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="25">
@@ -4702,11 +4731,11 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="25">
@@ -4719,14 +4748,14 @@
         <v>1030160</v>
       </c>
       <c r="B52" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="25" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="25">
@@ -4742,11 +4771,11 @@
         <v>0</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="25"/>
@@ -4758,11 +4787,13 @@
       <c r="A54" s="25">
         <v>1030180</v>
       </c>
-      <c r="B54" s="3"/>
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="25">
@@ -4778,11 +4809,11 @@
         <v>0</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="25"/>
@@ -4798,11 +4829,11 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="25">
@@ -4818,11 +4849,11 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="25">
@@ -4838,11 +4869,11 @@
         <v>0</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="25">
@@ -4858,11 +4889,11 @@
         <v>0</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="25">
@@ -4878,11 +4909,11 @@
         <v>0</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="25">
@@ -4898,11 +4929,11 @@
         <v>0</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="25">
@@ -4914,13 +4945,15 @@
       <c r="A62" s="25">
         <v>1030260</v>
       </c>
-      <c r="B62" s="3"/>
+      <c r="B62" s="3">
+        <v>0</v>
+      </c>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="25">
@@ -4932,13 +4965,15 @@
       <c r="A63" s="25">
         <v>1030270</v>
       </c>
-      <c r="B63" s="3"/>
+      <c r="B63" s="3">
+        <v>0</v>
+      </c>
       <c r="C63" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="25">
@@ -4956,7 +4991,7 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="25">
@@ -4972,11 +5007,11 @@
         <v>0</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="25"/>
@@ -4992,11 +5027,11 @@
         <v>0</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="25">
@@ -5012,11 +5047,11 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="25">
@@ -5032,11 +5067,11 @@
         <v>0</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="25">
@@ -5052,11 +5087,11 @@
         <v>0</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="25" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="25"/>
@@ -5072,11 +5107,11 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="25">
@@ -5092,11 +5127,11 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="25">
@@ -5108,13 +5143,15 @@
       <c r="A72" s="25">
         <v>1030360</v>
       </c>
-      <c r="B72" s="3"/>
+      <c r="B72" s="3">
+        <v>0</v>
+      </c>
       <c r="C72" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="25">
@@ -5126,13 +5163,15 @@
       <c r="A73" s="25">
         <v>1030370</v>
       </c>
-      <c r="B73" s="3"/>
+      <c r="B73" s="3">
+        <v>0</v>
+      </c>
       <c r="C73" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="25">
@@ -5144,13 +5183,15 @@
       <c r="A74" s="25">
         <v>1030380</v>
       </c>
-      <c r="B74" s="3"/>
+      <c r="B74" s="3">
+        <v>0</v>
+      </c>
       <c r="C74" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="25">
@@ -5162,13 +5203,15 @@
       <c r="A75" s="25">
         <v>1030390</v>
       </c>
-      <c r="B75" s="3"/>
+      <c r="B75" s="3">
+        <v>0</v>
+      </c>
       <c r="C75" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="25">
@@ -5184,11 +5227,11 @@
         <v>0</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="25">
@@ -5204,11 +5247,11 @@
         <v>0</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="25">
@@ -5226,7 +5269,7 @@
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="25">
@@ -5238,13 +5281,15 @@
       <c r="A79" s="25">
         <v>1030430</v>
       </c>
-      <c r="B79" s="3"/>
+      <c r="B79" s="3">
+        <v>0</v>
+      </c>
       <c r="C79" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="25">
@@ -5256,13 +5301,15 @@
       <c r="A80" s="25">
         <v>1030440</v>
       </c>
-      <c r="B80" s="3"/>
+      <c r="B80" s="3">
+        <v>0</v>
+      </c>
       <c r="C80" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="25">
@@ -5274,13 +5321,15 @@
       <c r="A81" s="25">
         <v>1030450</v>
       </c>
-      <c r="B81" s="3"/>
+      <c r="B81" s="3">
+        <v>0</v>
+      </c>
       <c r="C81" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="25">
@@ -5296,11 +5345,11 @@
         <v>0</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="25">
@@ -5316,11 +5365,11 @@
         <v>0</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="25">
@@ -5336,11 +5385,11 @@
         <v>0</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="25">
@@ -5358,7 +5407,7 @@
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="25">
@@ -5374,11 +5423,11 @@
         <v>0</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="25">
@@ -5390,13 +5439,15 @@
       <c r="A87" s="25">
         <v>1030510</v>
       </c>
-      <c r="B87" s="3"/>
+      <c r="B87" s="3">
+        <v>0</v>
+      </c>
       <c r="C87" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="25">
@@ -5408,13 +5459,15 @@
       <c r="A88" s="25">
         <v>1030520</v>
       </c>
-      <c r="B88" s="3"/>
+      <c r="B88" s="3">
+        <v>0</v>
+      </c>
       <c r="C88" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="25">
@@ -5426,13 +5479,15 @@
       <c r="A89" s="25">
         <v>1030530</v>
       </c>
-      <c r="B89" s="3"/>
+      <c r="B89" s="3">
+        <v>0</v>
+      </c>
       <c r="C89" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="25">
@@ -5444,13 +5499,15 @@
       <c r="A90" s="25">
         <v>1030540</v>
       </c>
-      <c r="B90" s="3"/>
+      <c r="B90" s="3">
+        <v>0</v>
+      </c>
       <c r="C90" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="25">
@@ -5462,13 +5519,15 @@
       <c r="A91" s="25">
         <v>1030550</v>
       </c>
-      <c r="B91" s="3"/>
+      <c r="B91" s="3">
+        <v>0</v>
+      </c>
       <c r="C91" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="25">
@@ -5480,13 +5539,15 @@
       <c r="A92" s="25">
         <v>1030560</v>
       </c>
-      <c r="B92" s="3"/>
+      <c r="B92" s="3">
+        <v>0</v>
+      </c>
       <c r="C92" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="25">
@@ -5504,7 +5565,7 @@
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="25">
@@ -5516,13 +5577,15 @@
       <c r="A94" s="25">
         <v>1030580</v>
       </c>
-      <c r="B94" s="3"/>
+      <c r="B94" s="3">
+        <v>0</v>
+      </c>
       <c r="C94" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="25">
@@ -5538,11 +5601,11 @@
         <v>0</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="25" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="25">
@@ -5558,11 +5621,11 @@
         <v>0</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="25"/>
@@ -5580,7 +5643,7 @@
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="45" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="25">
@@ -5596,11 +5659,11 @@
         <v>0</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="25">
@@ -5616,11 +5679,11 @@
         <v>0</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="25">
@@ -5632,13 +5695,15 @@
       <c r="A100" s="25">
         <v>1030640</v>
       </c>
-      <c r="B100" s="3"/>
+      <c r="B100" s="3">
+        <v>0</v>
+      </c>
       <c r="C100" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="25">
@@ -5656,7 +5721,7 @@
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="25">
@@ -5672,11 +5737,11 @@
         <v>0</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="29" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="25">
@@ -5692,11 +5757,11 @@
         <v>0</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="25" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="25">
@@ -5712,11 +5777,11 @@
         <v>0</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="25" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="25">
@@ -5734,7 +5799,7 @@
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="25" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="25">
@@ -5750,11 +5815,11 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="25" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="25">
@@ -5770,11 +5835,11 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="25" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="25">
@@ -5787,15 +5852,15 @@
         <v>1030720</v>
       </c>
       <c r="B108" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="25"/>
       <c r="F108" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G108" s="25">
         <v>1030730</v>
@@ -5810,11 +5875,11 @@
         <v>0</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="25" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="25">
@@ -5830,11 +5895,11 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="25">
@@ -5850,11 +5915,11 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="25" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="25">
@@ -5870,11 +5935,11 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="25" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="25">
@@ -5890,11 +5955,11 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="25" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="25">
@@ -5910,11 +5975,11 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="25" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="25">
@@ -5930,11 +5995,11 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="25" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="25">
@@ -5950,11 +6015,11 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="25">
@@ -5970,11 +6035,11 @@
         <v>0</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="25" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="25">
@@ -5990,11 +6055,11 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="25" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="25">
@@ -6010,11 +6075,11 @@
         <v>0</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="25" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="25">
@@ -6030,11 +6095,11 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="25" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="25">
@@ -6050,11 +6115,11 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="25" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="25">
@@ -6070,11 +6135,11 @@
         <v>0</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="25" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="25">
@@ -6090,11 +6155,11 @@
         <v>0</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="25" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="25">
@@ -6110,11 +6175,11 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="25" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="25">
@@ -6130,11 +6195,11 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="25" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="25">
@@ -6150,11 +6215,11 @@
         <v>0</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="25" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="25">
@@ -6170,11 +6235,11 @@
         <v>0</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="25" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="25">
@@ -6190,11 +6255,11 @@
         <v>0</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="25" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="25">
@@ -6210,11 +6275,11 @@
         <v>0</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="25" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="25">
@@ -6230,11 +6295,11 @@
         <v>0</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="25" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="25">
@@ -6252,7 +6317,7 @@
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="25" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="25">
@@ -6268,11 +6333,11 @@
         <v>0</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="25" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="25">
@@ -6288,11 +6353,11 @@
         <v>0</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="25" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="25">
@@ -6308,11 +6373,11 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="25" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F134" s="3"/>
       <c r="G134" s="25">
@@ -6328,11 +6393,11 @@
         <v>0</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="25" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="25">
@@ -6348,11 +6413,11 @@
         <v>0</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="25" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="25">
@@ -6368,11 +6433,11 @@
         <v>0</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="25" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="25">
@@ -6391,7 +6456,7 @@
       <c r="D138" s="3"/>
       <c r="E138" s="25"/>
       <c r="F138" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G138" s="25">
         <v>1031030</v>
@@ -6406,11 +6471,11 @@
         <v>0</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="25" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="25">
@@ -6426,11 +6491,11 @@
         <v>0</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="25" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="25">
@@ -6446,11 +6511,11 @@
         <v>0</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="25" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="25">
@@ -6466,11 +6531,11 @@
         <v>0</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="25" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="25">
@@ -6486,11 +6551,11 @@
         <v>0</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="25" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="25">
@@ -6506,11 +6571,11 @@
         <v>0</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="25" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="25">
@@ -6528,7 +6593,7 @@
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="25" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="25">
@@ -6544,11 +6609,11 @@
         <v>0</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="25" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="25">
@@ -6564,11 +6629,11 @@
         <v>0</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="25" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="25">
@@ -6584,11 +6649,11 @@
         <v>0</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D148" s="3"/>
       <c r="E148" s="25" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="25">
@@ -6604,11 +6669,11 @@
         <v>0</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="25" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="25">
@@ -6624,11 +6689,11 @@
         <v>0</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="25" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="25">
@@ -6646,7 +6711,7 @@
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="25" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F151" s="3"/>
       <c r="G151" s="25">
@@ -6662,11 +6727,11 @@
         <v>0</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="25" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="F152" s="3"/>
       <c r="G152" s="25">
@@ -6682,11 +6747,11 @@
         <v>0</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="25" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="25">
@@ -6704,7 +6769,7 @@
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="25">
@@ -6722,7 +6787,7 @@
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -6740,7 +6805,7 @@
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="45" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="25">
@@ -6758,7 +6823,7 @@
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="25">
@@ -6774,11 +6839,11 @@
         <v>0</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="25">
@@ -6794,11 +6859,11 @@
         <v>0</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="25">
@@ -6816,7 +6881,7 @@
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="25">
@@ -6834,7 +6899,7 @@
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="25">
@@ -6850,11 +6915,11 @@
         <v>0</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="25">
@@ -6870,11 +6935,11 @@
         <v>0</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="3" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="25">
@@ -6890,11 +6955,11 @@
         <v>0</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="3" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="25">
@@ -6910,11 +6975,11 @@
         <v>0</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="3" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="25">
@@ -6930,11 +6995,11 @@
         <v>0</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="3" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="25">
@@ -6950,11 +7015,11 @@
         <v>0</v>
       </c>
       <c r="C167" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="3" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="25">
@@ -6970,11 +7035,11 @@
         <v>0</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="25">
@@ -6992,7 +7057,7 @@
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="25">
@@ -7010,7 +7075,7 @@
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="25">
@@ -7026,11 +7091,11 @@
         <v>0</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="25">
@@ -7046,11 +7111,11 @@
         <v>0</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="25">
@@ -7066,11 +7131,11 @@
         <v>0</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="25">
@@ -7086,11 +7151,11 @@
         <v>0</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="25">
@@ -7106,11 +7171,11 @@
         <v>0</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D175" s="3"/>
       <c r="E175" s="3" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="25">
@@ -7126,11 +7191,11 @@
         <v>0</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="25">
@@ -7146,11 +7211,11 @@
         <v>0</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="25">
@@ -7166,11 +7231,11 @@
         <v>0</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="25">
@@ -7186,11 +7251,11 @@
         <v>0</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="25">
@@ -7208,7 +7273,7 @@
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="25">
@@ -7224,11 +7289,11 @@
         <v>0</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="25">
@@ -7244,11 +7309,11 @@
         <v>0</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="3" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="25">
@@ -7266,7 +7331,7 @@
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="25">
@@ -7282,11 +7347,11 @@
         <v>0</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D184" s="3"/>
       <c r="E184" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="25">
@@ -7302,11 +7367,11 @@
         <v>0</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="3" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="25">
@@ -7322,11 +7387,11 @@
         <v>0</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="3" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="25">
@@ -7342,11 +7407,11 @@
         <v>0</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="25">
@@ -7364,7 +7429,7 @@
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="25">
@@ -7380,11 +7445,11 @@
         <v>0</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="25">
@@ -7400,11 +7465,11 @@
         <v>0</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="25">
@@ -7420,11 +7485,11 @@
         <v>0</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D191" s="3"/>
       <c r="E191" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="25">
@@ -7440,11 +7505,11 @@
         <v>0</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="25">
@@ -7460,11 +7525,11 @@
         <v>0</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="25">
@@ -7480,11 +7545,11 @@
         <v>0</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="3" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="25">
@@ -7500,11 +7565,11 @@
         <v>0</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="3" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="25">
@@ -7520,11 +7585,11 @@
         <v>0</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="3" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="25">
@@ -7540,11 +7605,11 @@
         <v>0</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="25">
@@ -7560,11 +7625,11 @@
         <v>0</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="3" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="25">
@@ -7580,11 +7645,11 @@
         <v>0</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="3" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="25">
@@ -7600,11 +7665,11 @@
         <v>0</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D200" s="3"/>
       <c r="E200" s="3" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="25">
@@ -7620,11 +7685,11 @@
         <v>0</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D201" s="3"/>
       <c r="E201" s="3" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="25">
@@ -7640,11 +7705,11 @@
         <v>0</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="25">
@@ -7660,11 +7725,11 @@
         <v>0</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D203" s="3"/>
       <c r="E203" s="3" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="25">
@@ -7680,11 +7745,11 @@
         <v>0</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D204" s="3"/>
       <c r="E204" s="3" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="25">
@@ -7700,11 +7765,11 @@
         <v>0</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="3" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="25">
@@ -7720,11 +7785,11 @@
         <v>0</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="3" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="25">
@@ -7742,7 +7807,7 @@
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="25">
@@ -7758,11 +7823,11 @@
         <v>0</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="3" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="25">
@@ -7780,7 +7845,7 @@
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="25">
@@ -7796,11 +7861,11 @@
         <v>0</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="25">
@@ -7816,11 +7881,11 @@
         <v>0</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="3" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="25">
@@ -7836,11 +7901,11 @@
         <v>0</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="25">
@@ -7856,11 +7921,11 @@
         <v>0</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="3" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="25">
@@ -7876,11 +7941,11 @@
         <v>0</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="25">
@@ -7896,11 +7961,11 @@
         <v>0</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="25">
@@ -7916,11 +7981,11 @@
         <v>0</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="25">
@@ -7938,7 +8003,7 @@
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="25">
@@ -7956,7 +8021,7 @@
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="25">
@@ -7972,11 +8037,11 @@
         <v>0</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="25">
@@ -7992,11 +8057,11 @@
         <v>0</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="25">
@@ -8012,11 +8077,11 @@
         <v>0</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="25">
@@ -8032,11 +8097,11 @@
         <v>0</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="3" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="25">
@@ -8052,11 +8117,11 @@
         <v>0</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="3" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="25">
@@ -8072,11 +8137,11 @@
         <v>0</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="3" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="25">
@@ -8092,11 +8157,11 @@
         <v>0</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D225" s="3"/>
       <c r="E225" s="3" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="25">
@@ -8112,11 +8177,11 @@
         <v>0</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="3" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="25">
@@ -8132,11 +8197,11 @@
         <v>0</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="3" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="25">
@@ -8152,11 +8217,11 @@
         <v>0</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="25">
@@ -8174,7 +8239,7 @@
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="25">
@@ -8192,7 +8257,7 @@
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="25">
@@ -8208,11 +8273,11 @@
         <v>0</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="25">
@@ -8228,11 +8293,11 @@
         <v>0</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="25">
@@ -8248,11 +8313,11 @@
         <v>0</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="3" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="25">
@@ -8270,7 +8335,7 @@
       <c r="C234" s="25"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="25">
@@ -8286,11 +8351,11 @@
         <v>0</v>
       </c>
       <c r="C235" s="25" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="25" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="25">
@@ -8308,7 +8373,7 @@
       <c r="C236" s="25"/>
       <c r="D236" s="3"/>
       <c r="E236" s="25" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="25">
@@ -8326,7 +8391,7 @@
       <c r="C237" s="25"/>
       <c r="D237" s="3"/>
       <c r="E237" s="25" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="25">
@@ -8342,11 +8407,11 @@
         <v>0</v>
       </c>
       <c r="C238" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="25" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="25">
@@ -8362,11 +8427,11 @@
         <v>0</v>
       </c>
       <c r="C239" s="25" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D239" s="3"/>
       <c r="E239" s="25" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="25">
@@ -8384,7 +8449,7 @@
       <c r="C240" s="25"/>
       <c r="D240" s="3"/>
       <c r="E240" s="25" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="25">
@@ -8402,7 +8467,7 @@
       <c r="C241" s="25"/>
       <c r="D241" s="3"/>
       <c r="E241" s="25" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="25">
@@ -8418,11 +8483,11 @@
         <v>0</v>
       </c>
       <c r="C242" s="25" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="25" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -8438,11 +8503,11 @@
         <v>0</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="25" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="25">
@@ -8458,11 +8523,11 @@
         <v>0</v>
       </c>
       <c r="C244" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="25" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="25"/>
@@ -8480,7 +8545,7 @@
       <c r="C245" s="25"/>
       <c r="D245" s="3"/>
       <c r="E245" s="25" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="25">
@@ -8496,11 +8561,11 @@
         <v>0</v>
       </c>
       <c r="C246" s="25" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="25" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="25">
@@ -8516,11 +8581,11 @@
         <v>0</v>
       </c>
       <c r="C247" s="25" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="25" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="25">
@@ -8536,11 +8601,11 @@
         <v>0</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="25" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="25">
@@ -8558,7 +8623,7 @@
       <c r="C249" s="25"/>
       <c r="D249" s="3"/>
       <c r="E249" s="25" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="25">
@@ -8576,7 +8641,7 @@
       <c r="C250" s="25"/>
       <c r="D250" s="3"/>
       <c r="E250" s="25" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="25">
@@ -8594,7 +8659,7 @@
       <c r="C251" s="25"/>
       <c r="D251" s="3"/>
       <c r="E251" s="25" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="25">
@@ -8612,7 +8677,7 @@
       <c r="C252" s="25"/>
       <c r="D252" s="3"/>
       <c r="E252" s="25" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="25"/>
@@ -8628,7 +8693,7 @@
       <c r="C253" s="25"/>
       <c r="D253" s="3"/>
       <c r="E253" s="25" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="25">
@@ -8644,11 +8709,11 @@
         <v>0</v>
       </c>
       <c r="C254" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="25" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="25">
@@ -8664,11 +8729,11 @@
         <v>0</v>
       </c>
       <c r="C255" s="25" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="25" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="25">
@@ -8686,7 +8751,7 @@
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="25" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="25">
@@ -8704,7 +8769,7 @@
       <c r="C257" s="25"/>
       <c r="D257" s="3"/>
       <c r="E257" s="25" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="25">
@@ -8722,7 +8787,7 @@
       <c r="C258" s="25"/>
       <c r="D258" s="3"/>
       <c r="E258" s="25" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="25"/>
@@ -8738,7 +8803,7 @@
       <c r="C259" s="25"/>
       <c r="D259" s="3"/>
       <c r="E259" s="25" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -8754,11 +8819,11 @@
         <v>0</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="25" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="25">
@@ -8774,11 +8839,11 @@
         <v>0</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="25" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="25">
@@ -8796,7 +8861,7 @@
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="25" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F262" s="3"/>
       <c r="G262" s="25">
@@ -8812,11 +8877,11 @@
         <v>0</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="25">
@@ -8832,11 +8897,11 @@
         <v>0</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="3" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="25">
@@ -8852,11 +8917,11 @@
         <v>0</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D265" s="3"/>
       <c r="E265" s="3" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="25">
@@ -8872,11 +8937,11 @@
         <v>0</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="3" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="25">
@@ -8892,11 +8957,11 @@
         <v>0</v>
       </c>
       <c r="C267" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="3" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="25">
@@ -8914,7 +8979,7 @@
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="25">
@@ -8932,7 +8997,7 @@
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="25">
@@ -8948,11 +9013,11 @@
         <v>0</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="3" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="25">
@@ -8968,11 +9033,11 @@
         <v>0</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D271" s="3"/>
       <c r="E271" s="3" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="25">
@@ -8988,11 +9053,11 @@
         <v>0</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D272" s="3"/>
       <c r="E272" s="3" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="25">
@@ -9008,11 +9073,11 @@
         <v>0</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="25">
@@ -9030,7 +9095,7 @@
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="25">
@@ -9048,7 +9113,7 @@
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="25">
@@ -9060,11 +9125,13 @@
       <c r="A276" s="25">
         <v>1040340</v>
       </c>
-      <c r="B276" s="3"/>
+      <c r="B276" s="3">
+        <v>2</v>
+      </c>
       <c r="C276" s="25"/>
       <c r="D276" s="3"/>
       <c r="E276" s="25" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="25">
@@ -9082,7 +9149,7 @@
       <c r="C277" s="25"/>
       <c r="D277" s="3"/>
       <c r="E277" s="25" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="25">
@@ -9100,7 +9167,7 @@
       <c r="C278" s="25"/>
       <c r="D278" s="3"/>
       <c r="E278" s="25" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3"/>
@@ -9169,7 +9236,7 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F2" s="3">
         <v>1020190</v>
@@ -9187,7 +9254,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="32" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F3" s="3">
         <v>1020260</v>
@@ -9200,20 +9267,20 @@
         <v>10201</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
         <v>1030140</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="H4" s="3"/>
     </row>
@@ -9243,7 +9310,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F6" s="25">
         <v>1030180</v>
@@ -9256,16 +9323,16 @@
         <v>10202</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="F7" s="3">
         <v>1030610</v>
@@ -9278,22 +9345,22 @@
         <v>10202</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="F8" s="3">
         <v>1031200</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -9302,13 +9369,13 @@
         <v>10203</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3">
@@ -9338,13 +9405,13 @@
         <v>10204</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="25">
@@ -9381,10 +9448,10 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -9399,10 +9466,10 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -9417,10 +9484,10 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="66" x14ac:dyDescent="0.3">
@@ -9428,13 +9495,13 @@
         <v>10208</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3">
@@ -9464,23 +9531,23 @@
         <v>10209</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="25">
         <v>1040030</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -9488,23 +9555,23 @@
         <v>10209</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="25">
         <v>1040110</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -9515,20 +9582,20 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="25">
         <v>1040170</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -9536,13 +9603,13 @@
         <v>10210</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3">
@@ -9799,7 +9866,7 @@
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="F2" s="37"/>
       <c r="G2" s="37">
@@ -9815,11 +9882,11 @@
         <v>0</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D3" s="37"/>
       <c r="E3" s="37" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="F3" s="37"/>
       <c r="G3" s="37">
@@ -9837,7 +9904,7 @@
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
       <c r="E4" s="37" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="F4" s="37"/>
       <c r="G4" s="37">
@@ -9853,11 +9920,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D5" s="37"/>
       <c r="E5" s="37" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="F5" s="37"/>
       <c r="G5" s="37">
@@ -9873,11 +9940,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D6" s="37"/>
       <c r="E6" s="37" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="F6" s="37"/>
       <c r="G6" s="37">
@@ -9893,11 +9960,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D7" s="37"/>
       <c r="E7" s="37" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37">
@@ -9915,7 +9982,7 @@
       <c r="C8" s="37"/>
       <c r="D8" s="37"/>
       <c r="E8" s="37" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
@@ -9933,7 +10000,7 @@
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
       <c r="E9" s="37" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="F9" s="37"/>
       <c r="G9" s="37">
@@ -9949,11 +10016,11 @@
         <v>0</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="37" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="37">
@@ -9969,11 +10036,11 @@
         <v>0</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="37" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F11" s="37"/>
       <c r="G11" s="37">
@@ -9991,7 +10058,7 @@
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
       <c r="E12" s="37" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="37">
@@ -10007,11 +10074,11 @@
         <v>0</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="37">
@@ -10027,11 +10094,11 @@
         <v>0</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="37" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="37">
@@ -10049,7 +10116,7 @@
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
       <c r="E15" s="37" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F15" s="37"/>
       <c r="G15" s="37">
@@ -10067,7 +10134,7 @@
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="37">
@@ -10083,11 +10150,11 @@
         <v>0</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="37">
@@ -10105,7 +10172,7 @@
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
       <c r="E18" s="37" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
@@ -10123,7 +10190,7 @@
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="37">
@@ -10139,11 +10206,11 @@
         <v>0</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="37" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37">
@@ -10159,11 +10226,11 @@
         <v>0</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="37" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="F21" s="37"/>
       <c r="G21" s="37">
@@ -10181,7 +10248,7 @@
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
       <c r="E22" s="40" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="F22" s="37"/>
       <c r="G22" s="37">
@@ -10197,11 +10264,11 @@
         <v>0</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D23" s="37"/>
       <c r="E23" s="40" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="37">
@@ -10217,11 +10284,11 @@
         <v>0</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="40" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="37">
@@ -10237,11 +10304,11 @@
         <v>0</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="40" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="F25" s="37"/>
       <c r="G25" s="37">
@@ -10257,11 +10324,11 @@
         <v>0</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="40" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="F26" s="37"/>
       <c r="G26" s="37">
@@ -10279,7 +10346,7 @@
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
       <c r="E27" s="37" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
@@ -10297,7 +10364,7 @@
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
       <c r="E28" s="37" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="F28" s="37"/>
       <c r="G28" s="37">
@@ -10313,11 +10380,11 @@
         <v>0</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="37" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="F29" s="37"/>
       <c r="G29" s="37">
@@ -10333,11 +10400,11 @@
         <v>0</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="37" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="F30" s="37"/>
       <c r="G30" s="37">
@@ -10353,11 +10420,11 @@
         <v>0</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D31" s="37"/>
-      <c r="E31" s="37" t="s">
-        <v>463</v>
+      <c r="E31" s="40" t="s">
+        <v>593</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="37">
@@ -10375,7 +10442,7 @@
       <c r="C32" s="37"/>
       <c r="D32" s="37"/>
       <c r="E32" s="37" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="37">
@@ -10391,11 +10458,11 @@
         <v>0</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D33" s="37"/>
-      <c r="E33" s="37" t="s">
-        <v>466</v>
+      <c r="E33" s="40" t="s">
+        <v>595</v>
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="37">
@@ -10411,11 +10478,11 @@
         <v>0</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D34" s="37"/>
-      <c r="E34" s="37" t="s">
-        <v>467</v>
+      <c r="E34" s="40" t="s">
+        <v>596</v>
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="37">
@@ -10433,7 +10500,7 @@
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
       <c r="E35" s="37" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="37">
@@ -10449,11 +10516,11 @@
         <v>0</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D36" s="37"/>
       <c r="E36" s="37" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="F36" s="37"/>
       <c r="G36" s="37">
@@ -10469,11 +10536,11 @@
         <v>0</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D37" s="37"/>
-      <c r="E37" s="37" t="s">
-        <v>470</v>
+      <c r="E37" s="40" t="s">
+        <v>594</v>
       </c>
       <c r="F37" s="37"/>
       <c r="G37" s="37">
@@ -10491,7 +10558,7 @@
       <c r="C38" s="37"/>
       <c r="D38" s="37"/>
       <c r="E38" s="37" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="37">
@@ -10507,11 +10574,11 @@
         <v>0</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D39" s="37"/>
-      <c r="E39" s="37" t="s">
-        <v>472</v>
+      <c r="E39" s="40" t="s">
+        <v>597</v>
       </c>
       <c r="F39" s="37"/>
       <c r="G39" s="37">
@@ -10527,11 +10594,11 @@
         <v>0</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D40" s="37"/>
-      <c r="E40" s="37" t="s">
-        <v>473</v>
+      <c r="E40" s="40" t="s">
+        <v>598</v>
       </c>
       <c r="F40" s="37"/>
       <c r="G40" s="37">
@@ -10544,12 +10611,12 @@
         <v>1060230</v>
       </c>
       <c r="B41" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
-      <c r="E41" s="37" t="s">
-        <v>474</v>
+      <c r="E41" s="40" t="s">
+        <v>600</v>
       </c>
       <c r="F41" s="37"/>
       <c r="G41" s="37"/>
@@ -10567,7 +10634,7 @@
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
       <c r="E42" s="37" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="F42" s="37"/>
       <c r="G42" s="37">
@@ -10583,11 +10650,11 @@
         <v>0</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D43" s="37"/>
       <c r="E43" s="37" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="F43" s="37"/>
       <c r="G43" s="37">
@@ -10603,11 +10670,11 @@
         <v>0</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D44" s="37"/>
       <c r="E44" s="37" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="F44" s="37"/>
       <c r="G44" s="37">
@@ -10623,11 +10690,11 @@
         <v>0</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="37">
@@ -10643,11 +10710,11 @@
         <v>0</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D46" s="37"/>
       <c r="E46" s="37" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="37">
@@ -10665,7 +10732,7 @@
       <c r="C47" s="37"/>
       <c r="D47" s="37"/>
       <c r="E47" s="37" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="F47" s="37"/>
       <c r="G47" s="37">
@@ -10681,11 +10748,11 @@
         <v>0</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D48" s="37"/>
       <c r="E48" s="37" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="F48" s="37"/>
       <c r="G48" s="37">
@@ -10701,11 +10768,11 @@
         <v>0</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D49" s="37"/>
       <c r="E49" s="37" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="F49" s="37"/>
       <c r="G49" s="37">
@@ -10723,7 +10790,7 @@
       <c r="C50" s="37"/>
       <c r="D50" s="37"/>
       <c r="E50" s="37" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="F50" s="37"/>
       <c r="G50" s="37"/>
@@ -10741,7 +10808,7 @@
       <c r="C51" s="37"/>
       <c r="D51" s="37"/>
       <c r="E51" s="37" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="F51" s="37"/>
       <c r="G51" s="37">
@@ -10757,11 +10824,11 @@
         <v>0</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D52" s="37"/>
       <c r="E52" s="37" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="F52" s="37"/>
       <c r="G52" s="37">
@@ -10777,11 +10844,11 @@
         <v>0</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D53" s="37"/>
       <c r="E53" s="37" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="F53" s="37"/>
       <c r="G53" s="37">
@@ -10799,7 +10866,7 @@
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
       <c r="E54" s="37" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="F54" s="37"/>
       <c r="G54" s="37">
@@ -10817,7 +10884,7 @@
       <c r="C55" s="37"/>
       <c r="D55" s="37"/>
       <c r="E55" s="37" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="F55" s="37"/>
       <c r="G55" s="37">
@@ -10833,11 +10900,11 @@
         <v>0</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D56" s="37"/>
       <c r="E56" s="37" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="F56" s="37"/>
       <c r="G56" s="37">
@@ -10853,11 +10920,11 @@
         <v>0</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D57" s="37"/>
       <c r="E57" s="37" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="F57" s="37"/>
       <c r="G57" s="37">
@@ -10873,11 +10940,11 @@
         <v>0</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D58" s="37"/>
       <c r="E58" s="37" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="F58" s="37"/>
       <c r="G58" s="37">
@@ -10895,7 +10962,7 @@
       <c r="C59" s="37"/>
       <c r="D59" s="37"/>
       <c r="E59" s="37" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="F59" s="37"/>
       <c r="G59" s="37">
@@ -10911,11 +10978,11 @@
         <v>0</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D60" s="37"/>
       <c r="E60" s="37" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="F60" s="37"/>
       <c r="G60" s="37">
@@ -10931,11 +10998,11 @@
         <v>0</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D61" s="37"/>
       <c r="E61" s="37" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="F61" s="37"/>
       <c r="G61" s="37">
@@ -10953,7 +11020,7 @@
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
@@ -10971,7 +11038,7 @@
       <c r="C63" s="37"/>
       <c r="D63" s="37"/>
       <c r="E63" s="37" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="F63" s="37"/>
       <c r="G63" s="37">
@@ -10987,11 +11054,11 @@
         <v>0</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="D64" s="37"/>
       <c r="E64" s="37" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="F64" s="37"/>
       <c r="G64" s="37">
@@ -11009,7 +11076,7 @@
       <c r="C65" s="37"/>
       <c r="D65" s="37"/>
       <c r="E65" s="37" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F65" s="37"/>
       <c r="G65" s="37">
@@ -11025,11 +11092,11 @@
         <v>0</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="D66" s="37"/>
       <c r="E66" s="37" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="F66" s="37"/>
       <c r="G66" s="37">
@@ -11045,11 +11112,11 @@
         <v>0</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D67" s="37"/>
       <c r="E67" s="37" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="F67" s="37"/>
       <c r="G67" s="37">
@@ -11065,11 +11132,11 @@
         <v>0</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D68" s="37"/>
       <c r="E68" s="37" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="F68" s="37"/>
       <c r="G68" s="37">
@@ -11087,7 +11154,7 @@
       <c r="C69" s="37"/>
       <c r="D69" s="37"/>
       <c r="E69" s="37" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="F69" s="37"/>
       <c r="G69" s="37"/>
@@ -11105,7 +11172,7 @@
       <c r="C70" s="37"/>
       <c r="D70" s="37"/>
       <c r="E70" s="37" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F70" s="37"/>
       <c r="G70" s="37">
@@ -11121,11 +11188,11 @@
         <v>0</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D71" s="37"/>
       <c r="E71" s="37" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="F71" s="37"/>
       <c r="G71" s="37">
@@ -11141,11 +11208,11 @@
         <v>0</v>
       </c>
       <c r="C72" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D72" s="37"/>
       <c r="E72" s="37" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="F72" s="37"/>
       <c r="G72" s="37">
@@ -11163,7 +11230,7 @@
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
       <c r="E73" s="37" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="F73" s="37"/>
       <c r="G73" s="37">
@@ -11179,11 +11246,11 @@
         <v>0</v>
       </c>
       <c r="C74" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D74" s="37"/>
       <c r="E74" s="37" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="F74" s="37"/>
       <c r="G74" s="37">
@@ -11201,7 +11268,7 @@
       <c r="C75" s="37"/>
       <c r="D75" s="37"/>
       <c r="E75" s="37" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="F75" s="37"/>
       <c r="G75" s="37">
@@ -11219,7 +11286,7 @@
       <c r="C76" s="37"/>
       <c r="D76" s="37"/>
       <c r="E76" s="37" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="F76" s="37"/>
       <c r="G76" s="37">
@@ -11235,11 +11302,11 @@
         <v>0</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D77" s="37"/>
       <c r="E77" s="37" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="F77" s="37"/>
       <c r="G77" s="37">
@@ -11257,7 +11324,7 @@
       <c r="C78" s="37"/>
       <c r="D78" s="37"/>
       <c r="E78" s="37" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="F78" s="37"/>
       <c r="G78" s="37"/>
@@ -11275,7 +11342,7 @@
       <c r="C79" s="37"/>
       <c r="D79" s="37"/>
       <c r="E79" s="37" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="F79" s="37"/>
       <c r="G79" s="37">
@@ -11291,11 +11358,11 @@
         <v>0</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D80" s="37"/>
       <c r="E80" s="37" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="F80" s="37"/>
       <c r="G80" s="37">
@@ -11311,11 +11378,11 @@
         <v>0</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D81" s="37"/>
       <c r="E81" s="37" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="F81" s="37"/>
       <c r="G81" s="37">
@@ -11331,11 +11398,11 @@
         <v>0</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="D82" s="37"/>
       <c r="E82" s="37" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="F82" s="37"/>
       <c r="G82" s="37">
@@ -11351,11 +11418,11 @@
         <v>0</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="F83" s="37"/>
       <c r="G83" s="37">
@@ -11373,7 +11440,7 @@
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
       <c r="E84" s="37" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="F84" s="37"/>
       <c r="G84" s="37">
@@ -11391,7 +11458,7 @@
       <c r="C85" s="37"/>
       <c r="D85" s="37"/>
       <c r="E85" s="37" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="F85" s="37"/>
       <c r="G85" s="37">
@@ -11407,11 +11474,11 @@
         <v>0</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D86" s="37"/>
       <c r="E86" s="37" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="F86" s="37"/>
       <c r="G86" s="37">
@@ -11429,7 +11496,7 @@
       <c r="C87" s="37"/>
       <c r="D87" s="37"/>
       <c r="E87" s="37" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="F87" s="37"/>
       <c r="G87" s="37"/>
@@ -11447,7 +11514,7 @@
       <c r="C88" s="37"/>
       <c r="D88" s="37"/>
       <c r="E88" s="37" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="F88" s="37"/>
       <c r="G88" s="37">
@@ -11463,11 +11530,11 @@
         <v>0</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D89" s="37"/>
       <c r="E89" s="37" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="F89" s="37"/>
       <c r="G89" s="37">
@@ -11485,7 +11552,7 @@
       <c r="C90" s="37"/>
       <c r="D90" s="37"/>
       <c r="E90" s="37" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F90" s="37"/>
       <c r="G90" s="37">
@@ -11501,11 +11568,11 @@
         <v>0</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="D91" s="37"/>
       <c r="E91" s="37" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37">
@@ -11521,11 +11588,11 @@
         <v>0</v>
       </c>
       <c r="C92" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D92" s="37"/>
       <c r="E92" s="37" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="F92" s="37"/>
       <c r="G92" s="37">
@@ -11543,7 +11610,7 @@
       <c r="C93" s="37"/>
       <c r="D93" s="37"/>
       <c r="E93" s="37" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="F93" s="37"/>
       <c r="G93" s="37"/>
@@ -11561,7 +11628,7 @@
       <c r="C94" s="37"/>
       <c r="D94" s="37"/>
       <c r="E94" s="37" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="F94" s="37"/>
       <c r="G94" s="37">
@@ -11577,11 +11644,11 @@
         <v>0</v>
       </c>
       <c r="C95" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D95" s="37"/>
       <c r="E95" s="37" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="F95" s="37"/>
       <c r="G95" s="37">
@@ -11599,7 +11666,7 @@
       <c r="C96" s="37"/>
       <c r="D96" s="37"/>
       <c r="E96" s="37" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="F96" s="37"/>
       <c r="G96" s="37">
@@ -11615,11 +11682,11 @@
         <v>0</v>
       </c>
       <c r="C97" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D97" s="37"/>
       <c r="E97" s="37" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="F97" s="37"/>
       <c r="G97" s="37">
@@ -11635,11 +11702,11 @@
         <v>0</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D98" s="37"/>
       <c r="E98" s="37" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="F98" s="37"/>
       <c r="G98" s="37">
@@ -11655,11 +11722,11 @@
         <v>0</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D99" s="37"/>
       <c r="E99" s="37" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="F99" s="37"/>
       <c r="G99" s="37">
@@ -11675,11 +11742,11 @@
         <v>0</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D100" s="37"/>
       <c r="E100" s="37" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="F100" s="37"/>
       <c r="G100" s="37">
@@ -11695,11 +11762,11 @@
         <v>0</v>
       </c>
       <c r="C101" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D101" s="37"/>
       <c r="E101" s="37" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="F101" s="37"/>
       <c r="G101" s="37">
@@ -11717,7 +11784,7 @@
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
       <c r="E102" s="37" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
@@ -11735,7 +11802,7 @@
       <c r="C103" s="37"/>
       <c r="D103" s="37"/>
       <c r="E103" s="37" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="F103" s="37"/>
       <c r="G103" s="37">
@@ -11751,11 +11818,11 @@
         <v>0</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D104" s="37"/>
       <c r="E104" s="37" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="F104" s="37"/>
       <c r="G104" s="37">
@@ -11773,7 +11840,7 @@
       <c r="C105" s="37"/>
       <c r="D105" s="37"/>
       <c r="E105" s="37" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="F105" s="37"/>
       <c r="G105" s="37">
@@ -11791,7 +11858,7 @@
       <c r="C106" s="37"/>
       <c r="D106" s="37"/>
       <c r="E106" s="37" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="F106" s="37"/>
       <c r="G106" s="37">
@@ -11807,11 +11874,11 @@
         <v>0</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D107" s="37"/>
       <c r="E107" s="37" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="F107" s="37"/>
       <c r="G107" s="37">
@@ -11827,11 +11894,11 @@
         <v>0</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D108" s="37"/>
       <c r="E108" s="37" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="F108" s="37"/>
       <c r="G108" s="37">
@@ -11847,11 +11914,11 @@
         <v>0</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D109" s="37"/>
       <c r="E109" s="37" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="F109" s="37"/>
       <c r="G109" s="37">
@@ -11869,7 +11936,7 @@
       <c r="C110" s="37"/>
       <c r="D110" s="37"/>
       <c r="E110" s="37" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="F110" s="37"/>
       <c r="G110" s="37">
@@ -11885,11 +11952,11 @@
         <v>0</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D111" s="37"/>
       <c r="E111" s="37" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="F111" s="37"/>
       <c r="G111" s="37">
@@ -11905,11 +11972,11 @@
         <v>0</v>
       </c>
       <c r="C112" s="37" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D112" s="37"/>
       <c r="E112" s="37" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="F112" s="37"/>
       <c r="G112" s="37">
@@ -11927,7 +11994,7 @@
       <c r="C113" s="37"/>
       <c r="D113" s="37"/>
       <c r="E113" s="37" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="F113" s="37"/>
       <c r="G113" s="37">
@@ -11943,11 +12010,11 @@
         <v>0</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D114" s="37"/>
       <c r="E114" s="37" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="F114" s="37"/>
       <c r="G114" s="37">
@@ -11965,7 +12032,7 @@
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
       <c r="E115" s="37" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="F115" s="37"/>
       <c r="G115" s="37">
@@ -11983,7 +12050,7 @@
       <c r="C116" s="37"/>
       <c r="D116" s="37"/>
       <c r="E116" s="37" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F116" s="37"/>
       <c r="G116" s="37"/>
@@ -12030,7 +12097,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -12079,16 +12146,16 @@
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="F2" s="37">
         <v>1050080</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -12101,16 +12168,16 @@
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
       <c r="E3" s="37" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F3" s="37">
         <v>1050110</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -12125,10 +12192,10 @@
       <c r="E4" s="37"/>
       <c r="F4" s="37"/>
       <c r="G4" s="37" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -12141,16 +12208,16 @@
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
       <c r="E5" s="37" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="F5" s="37">
         <v>1060100</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -12163,16 +12230,14 @@
       <c r="C6" s="37"/>
       <c r="D6" s="37"/>
       <c r="E6" s="37" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="F6" s="37">
         <v>1060140</v>
       </c>
-      <c r="G6" s="37" t="s">
-        <v>561</v>
-      </c>
+      <c r="G6" s="37"/>
       <c r="H6" s="37" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -12180,26 +12245,26 @@
         <v>10601</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="F7" s="37">
         <v>1060170</v>
       </c>
       <c r="G7" s="37"/>
       <c r="H7" s="37" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>10602</v>
       </c>
@@ -12210,11 +12275,11 @@
       <c r="D8" s="37"/>
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
-      <c r="G8" s="37" t="s">
-        <v>566</v>
+      <c r="G8" s="40" t="s">
+        <v>599</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -12227,16 +12292,16 @@
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
       <c r="E9" s="37" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="F9" s="37">
         <v>1070100</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -12244,23 +12309,23 @@
         <v>10701</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="F10" s="37">
         <v>1070140</v>
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="37" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -12268,21 +12333,21 @@
         <v>10702</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="E11" s="37"/>
       <c r="F11" s="37"/>
       <c r="G11" s="40" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
@@ -12297,10 +12362,10 @@
       <c r="E12" s="37"/>
       <c r="F12" s="37"/>
       <c r="G12" s="40" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -12313,14 +12378,14 @@
       <c r="C13" s="37"/>
       <c r="D13" s="37"/>
       <c r="E13" s="37" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="F13" s="37">
         <v>1080080</v>
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -12333,14 +12398,14 @@
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
       <c r="E14" s="37" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="F14" s="37">
         <v>1080110</v>
       </c>
       <c r="G14" s="37"/>
       <c r="H14" s="37" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -12353,14 +12418,14 @@
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
       <c r="E15" s="37" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="F15" s="37">
         <v>1080140</v>
       </c>
       <c r="G15" s="37"/>
       <c r="H15" s="37" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -12375,10 +12440,10 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
       <c r="G16" s="37" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -12391,14 +12456,14 @@
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
       <c r="E17" s="37" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="F17" s="37">
         <v>1090100</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -12411,14 +12476,14 @@
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
       <c r="E18" s="37" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F18" s="37">
         <v>1090120</v>
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="37" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -12433,10 +12498,10 @@
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -12449,16 +12514,16 @@
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
       <c r="E20" s="37" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="F20" s="37">
         <v>1100100</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -12471,14 +12536,14 @@
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
       <c r="E21" s="37" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="F21" s="37">
         <v>1100130</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -12486,23 +12551,23 @@
         <v>11001</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="F22" s="37">
         <v>1100170</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.3">
@@ -12510,21 +12575,21 @@
         <v>11002</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
       <c r="G23" s="40" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
@@ -12539,10 +12604,15 @@
       <c r="E24" s="37"/>
       <c r="F24" s="37"/>
       <c r="G24" s="40" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>590</v>
+        <v>571</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="37">
+        <v>10601</v>
       </c>
     </row>
   </sheetData>
